--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104558_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104558_W12.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7276</v>
+        <v>7.7802</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2869</v>
+        <v>4.6543</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4407</v>
+        <v>3.1258</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5975</v>
+        <v>1.5823</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1601</v>
+        <v>2.1625</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5626</v>
+        <v>-0.5802</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1301</v>
+        <v>1.0922</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5168</v>
+        <v>1.5029</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.3867</v>
+        <v>-0.4107</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4674</v>
+        <v>0.4901</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6433</v>
+        <v>0.6597</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0789</v>
+        <v>0.1571</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6261</v>
+        <v>-0.2023</v>
       </c>
       <c r="U2" t="n">
-        <v>0.705</v>
+        <v>0.3594</v>
       </c>
       <c r="V2" t="n">
-        <v>4.917</v>
+        <v>4.9026</v>
       </c>
       <c r="W2" t="n">
-        <v>4.917</v>
+        <v>4.9026</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6526</v>
+        <v>4.4064</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3359</v>
+        <v>2.3262</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3168</v>
+        <v>2.0803</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6919</v>
+        <v>2.6907</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7114</v>
+        <v>0.7095</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9805</v>
+        <v>1.9812</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8278</v>
+        <v>1.8154</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6238</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1941</v>
+        <v>1.1916</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8641</v>
+        <v>0.8754</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8946</v>
+        <v>0.6458</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5081</v>
+        <v>0.5108</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3865</v>
+        <v>0.135</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3479</v>
+        <v>2.9674</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2979</v>
+        <v>1.011</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0499</v>
+        <v>1.9564</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6912</v>
+        <v>2.7084</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6116</v>
+        <v>1.6221</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0796</v>
+        <v>1.0862</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2556</v>
+        <v>2.2471</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4719</v>
+        <v>1.4651</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4356</v>
+        <v>0.4613</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1397</v>
+        <v>0.157</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6567</v>
+        <v>1.259</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3107</v>
+        <v>1.0402</v>
       </c>
       <c r="U4" t="n">
-        <v>0.346</v>
+        <v>0.2189</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9455</v>
+        <v>2.6314</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4168</v>
+        <v>1.8304</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5286</v>
+        <v>0.801</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5913</v>
+        <v>0.5989</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7895</v>
+        <v>-0.7789</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3807</v>
+        <v>1.3778</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2565</v>
+        <v>1.2431</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4573</v>
+        <v>-0.4621</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7139</v>
+        <v>1.7052</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6653</v>
+        <v>-0.6442</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>1.22</v>
+        <v>0.8944</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1603</v>
+        <v>0.5874</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0597</v>
+        <v>0.3071</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6318</v>
+        <v>2.4164</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5155</v>
+        <v>1.2522</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1163</v>
+        <v>1.1642</v>
       </c>
       <c r="G6" t="n">
-        <v>2.073</v>
+        <v>2.0574</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0994</v>
+        <v>-0.1114</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1724</v>
+        <v>2.1687</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2111</v>
+        <v>2.1861</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1772</v>
+        <v>-0.1971</v>
       </c>
       <c r="L6" t="n">
-        <v>2.3883</v>
+        <v>2.3832</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1381</v>
+        <v>-0.1287</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4927</v>
+        <v>0.2892</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4386</v>
+        <v>0.2042</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0541</v>
+        <v>0.0849</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8941</v>
+        <v>1.985</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6953</v>
+        <v>0.6359</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1988</v>
+        <v>1.349</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2001</v>
+        <v>1.2084</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7057</v>
+        <v>-0.6983</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9059</v>
+        <v>1.9067</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4604</v>
+        <v>1.4514</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4054</v>
+        <v>-0.4104</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8658</v>
+        <v>1.8618</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2603</v>
+        <v>-0.243</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0835</v>
+        <v>0.1604</v>
       </c>
       <c r="T7" t="n">
-        <v>0.369</v>
+        <v>0.3227</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2855</v>
+        <v>-0.1623</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3582</v>
+        <v>1.1008</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.3395</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2945</v>
+        <v>0.7613</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4203</v>
+        <v>0.4135</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0086</v>
+        <v>3.0071</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.5883</v>
+        <v>-2.5937</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8138</v>
+        <v>0.7839</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3248</v>
+        <v>3.3095</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.511</v>
+        <v>-2.5255</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3935</v>
+        <v>-0.3704</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4912</v>
+        <v>0.2532</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0212</v>
+        <v>0.3295</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5123</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.29</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5659999999999999</v>
+        <v>1.6324</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6399</v>
+        <v>-1.9224</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1846</v>
+        <v>0.5023</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0233</v>
+        <v>0.2031</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2079</v>
+        <v>0.2992</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5863</v>
+        <v>2.0649</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1039</v>
+        <v>1.2238</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4824</v>
+        <v>0.8411</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4017</v>
+        <v>-1.5626</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1272</v>
+        <v>-1.0207</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2745</v>
+        <v>-0.5419</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9073</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5846</v>
+        <v>0.079</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1553</v>
+        <v>0.4874</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5707</v>
+        <v>-0.4085</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06419999999999999</v>
+        <v>1.405</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>2.4945</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0285</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4022</v>
+        <v>-0.5493</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0045</v>
+        <v>-0.1566</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4067</v>
+        <v>-0.3927</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.323</v>
+        <v>0.1934</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0392</v>
+        <v>-0.0121</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3621</v>
+        <v>0.2055</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4736</v>
+        <v>0.5798</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1323</v>
+        <v>0.1034</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3413</v>
+        <v>0.4764</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8494</v>
+        <v>-0.3865</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1715</v>
+        <v>-0.1155</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0209</v>
+        <v>-0.271</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0549</v>
+        <v>0.0964</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9467</v>
+        <v>0.4504</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1083</v>
+        <v>-0.354</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5463</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7997</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>-1.018</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9077</v>
+        <v>-0.8784999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4215</v>
+        <v>-0.5647</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3292</v>
+        <v>-0.3137</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4926</v>
+        <v>-1.3396</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1888</v>
+        <v>0.0265</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3038</v>
+        <v>-1.3662</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0824</v>
+        <v>-0.5098</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2295</v>
+        <v>-0.1594</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8529</v>
+        <v>-0.3505</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5897</v>
+        <v>-0.8298</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0407</v>
+        <v>0.1859</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.549</v>
+        <v>-1.0157</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.2683</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5461</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7652</v>
+        <v>0.4294</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7809</v>
+        <v>0.1699</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4141</v>
+        <v>0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>2.5068</v>
+        <v>1.792</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8814</v>
+        <v>-2.1441</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2063</v>
+        <v>-2.6751</v>
       </c>
       <c r="F12" t="n">
-        <v>0.325</v>
+        <v>0.531</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4833</v>
+        <v>-0.4763</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6566</v>
+        <v>-0.6522</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1733</v>
+        <v>0.1759</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.6635</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1764</v>
+        <v>0.1871</v>
       </c>
       <c r="N12" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O12" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.398</v>
+        <v>0.3322</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2782</v>
+        <v>0.2647</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1198</v>
+        <v>0.0675</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.4816</v>
+        <v>-6.921</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.7074</v>
+        <v>-7.2022</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2258</v>
+        <v>0.2812</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.6977</v>
+        <v>-3.6982</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.5382</v>
+        <v>-2.5362</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1595</v>
+        <v>-1.162</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.5447</v>
+        <v>-2.5657</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.7184</v>
+        <v>-1.7312</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8264</v>
+        <v>-0.8345</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.153</v>
+        <v>-1.1325</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0619</v>
+        <v>-0.4912</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6261</v>
+        <v>-0.0838</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4358</v>
+        <v>-0.4074</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.8109</v>
+        <v>12.5047</v>
       </c>
       <c r="E14" t="n">
-        <v>2.690299999999997</v>
+        <v>3.083299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>9.120599999999998</v>
+        <v>9.4214</v>
       </c>
       <c r="G14" t="n">
-        <v>6.438499999999999</v>
+        <v>6.4412</v>
       </c>
       <c r="H14" t="n">
-        <v>2.907</v>
+        <v>2.941700000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>3.531600000000001</v>
+        <v>3.4991</v>
       </c>
       <c r="J14" t="n">
-        <v>9.9459</v>
+        <v>9.724900000000002</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6555</v>
+        <v>4.5304</v>
       </c>
       <c r="L14" t="n">
-        <v>5.2903</v>
+        <v>5.194599999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.5075</v>
+        <v>-3.2838</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7484</v>
+        <v>-1.5885</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7587</v>
+        <v>-1.6954</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.402399999999999</v>
+        <v>-3.4144</v>
       </c>
       <c r="Q14" t="n">
-        <v>-20.415</v>
+        <v>-20.4869</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0126</v>
+        <v>17.0726</v>
       </c>
       <c r="S14" t="n">
-        <v>3.568699999999999</v>
+        <v>4.274800000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>3.6143</v>
+        <v>4.3406</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.04540000000000016</v>
+        <v>-0.06580000000000003</v>
       </c>
       <c r="V14" t="n">
-        <v>5.205999999999999</v>
+        <v>5.2032</v>
       </c>
       <c r="W14" t="n">
-        <v>9.545</v>
+        <v>9.5047</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.3389</v>
+        <v>-4.3013</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5703</v>
+        <v>0.4097</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.8434</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3742</v>
+        <v>1.2531</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5154</v>
+        <v>1.5148</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4056</v>
+        <v>2.3931</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8902</v>
+        <v>-0.8783</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6979</v>
+        <v>2.672</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5487</v>
+        <v>2.5231</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1825</v>
+        <v>-1.1573</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.5794</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5111</v>
+        <v>0.5152</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2223</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3165</v>
+        <v>0.1981</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3969</v>
+        <v>-0.1336</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0805</v>
+        <v>0.3316</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.0013</v>
+        <v>-2.0179</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.2567</v>
+        <v>-3.2596</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2554</v>
+        <v>1.2417</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2944</v>
+        <v>-0.3423</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.5869</v>
+        <v>-1.6073</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2926</v>
+        <v>1.2649</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.707</v>
+        <v>-1.6756</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6698</v>
+        <v>-1.6524</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0372</v>
+        <v>-0.0232</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3212</v>
+        <v>-0.4182</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7743</v>
+        <v>0.3061</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0955</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2145</v>
+        <v>0.0504</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7897</v>
+        <v>-0.5784</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5752</v>
+        <v>0.6288</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6009</v>
+        <v>0.6006</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5556</v>
+        <v>0.5544</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0453</v>
+        <v>0.0462</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0185</v>
+        <v>1.0015</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1704</v>
+        <v>1.1581</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4176</v>
+        <v>-0.4009</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6547</v>
+        <v>-1.3925</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8347</v>
+        <v>-0.5995</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8199</v>
+        <v>-0.7929</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. ALMAZAN</t>
+          <t>Y. NZOSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7096</v>
+        <v>-0.3435</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4001</v>
+        <v>0.1454</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3096</v>
+        <v>-0.4888</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.089</v>
+        <v>-0.0482</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3449</v>
+        <v>-0.5399</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2559</v>
+        <v>0.4917</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0173</v>
+        <v>-0.0774</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0173</v>
+        <v>-0.1519</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0745</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1063</v>
+        <v>0.0292</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3622</v>
+        <v>-0.3881</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2559</v>
+        <v>0.4173</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8474</v>
+        <v>0.0626</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4174</v>
+        <v>0.2228</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4301</v>
+        <v>-0.1601</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y. NZOSA</t>
+          <t>P. ALMAZAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7842</v>
+        <v>-0.6424</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0861</v>
+        <v>-0.401</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6981000000000001</v>
+        <v>-0.2414</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0518</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5397</v>
+        <v>-0.3419</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4878</v>
+        <v>0.2593</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.0172</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1456</v>
+        <v>0.0172</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0746</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0192</v>
+        <v>-0.0998</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.394</v>
+        <v>-0.3592</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4132</v>
+        <v>0.2593</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3617</v>
+        <v>-0.7874</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0151</v>
+        <v>-0.4182</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3466</v>
+        <v>-0.3692</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. DE SOUSA</t>
+          <t>L. FISCHER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2081</v>
+        <v>-0.6828</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4031</v>
+        <v>0.1701</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6112</v>
+        <v>-0.8529</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4626</v>
+        <v>-1.7919</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0707</v>
+        <v>-0.0866</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3919</v>
+        <v>-1.7052</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3765</v>
+        <v>0.2841</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3392</v>
+        <v>0.1724</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>0.1117</v>
       </c>
       <c r="M20" t="n">
-        <v>0.08599999999999999</v>
+        <v>-2.0759</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3546</v>
+        <v>-1.8169</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3285</v>
+        <v>-0.208</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0907</v>
+        <v>-0.0653</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4192</v>
+        <v>-0.1427</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.2495</v>
+        <v>1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.06419999999999999</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. MEINDL</t>
+          <t>J. AXEL GUDMUNDSSON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2294</v>
+        <v>-1.3079</v>
       </c>
       <c r="E21" t="n">
-        <v>0.461</v>
+        <v>-2.8733</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6904</v>
+        <v>1.5654</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6123</v>
+        <v>-1.6129</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2231</v>
+        <v>-0.7179</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3892</v>
+        <v>-0.895</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0566</v>
+        <v>-1.1583</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.3946</v>
+        <v>-1.0762</v>
       </c>
       <c r="L21" t="n">
-        <v>1.338</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5557</v>
+        <v>-0.4546</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1715</v>
+        <v>0.3583</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7272</v>
+        <v>-0.8129</v>
       </c>
       <c r="P21" t="n">
-        <v>2.722</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>2.722</v>
+        <v>3.1868</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8462</v>
+        <v>0.3262</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8106</v>
+        <v>0.4036</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0357</v>
+        <v>-0.0774</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1853</v>
+        <v>-0.9317</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7071</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.8924</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. FISCHER</t>
+          <t>S. DE SOUSA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.326</v>
+        <v>-1.6807</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2947</v>
+        <v>0.0338</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0313</v>
+        <v>-1.7145</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8092</v>
+        <v>0.4697</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0954</v>
+        <v>0.0717</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7139</v>
+        <v>0.398</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2851</v>
+        <v>0.368</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1732</v>
+        <v>0.3308</v>
       </c>
       <c r="L22" t="n">
-        <v>0.112</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0944</v>
+        <v>0.1018</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.8258</v>
+        <v>0.3608</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8363</v>
+        <v>-0.8106</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5383</v>
+        <v>-0.2627</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2979</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>1.0927</v>
+        <v>-2.2504</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. AXEL GUDMUNDSSON</t>
+          <t>L. MEINDL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4588</v>
+        <v>-1.9654</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0819</v>
+        <v>-0.068</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6231</v>
+        <v>-1.8974</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6166</v>
+        <v>-2.6433</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7157</v>
+        <v>-2.2529</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9009</v>
+        <v>-0.3903</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1377</v>
+        <v>-1.1137</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.0603</v>
+        <v>-2.4388</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.07729999999999999</v>
+        <v>1.3252</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4789</v>
+        <v>-1.5296</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3446</v>
+        <v>0.1859</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8236</v>
+        <v>-1.7155</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9073</v>
+        <v>2.7316</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.1757</v>
+        <v>2.7316</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1824</v>
+        <v>0.1253</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1633</v>
+        <v>0.3432</v>
       </c>
       <c r="U23" t="n">
-        <v>0.019</v>
+        <v>-0.2179</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0.7025</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4457</v>
+        <v>-2.9072</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.924</v>
+        <v>-1.4113</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5217</v>
+        <v>-1.4959</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2286</v>
+        <v>-1.2232</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1601</v>
+        <v>0.1635</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.3887</v>
+        <v>-1.3867</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0379</v>
+        <v>-0.0499</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1141</v>
+        <v>0.1067</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1908</v>
+        <v>-1.1733</v>
       </c>
       <c r="N24" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2368</v>
+        <v>-1.2301</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0363</v>
+        <v>-0.4367</v>
       </c>
       <c r="T24" t="n">
-        <v>0.248</v>
+        <v>-0.2232</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2117</v>
+        <v>-0.2135</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.3214</v>
+        <v>-2.9361</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0014</v>
+        <v>-3.4617</v>
       </c>
       <c r="F25" t="n">
-        <v>0.68</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3915</v>
+        <v>0.3937</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0765</v>
+        <v>1.0743</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.6806</v>
       </c>
       <c r="J25" t="n">
-        <v>1.7094</v>
+        <v>1.6825</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5731</v>
+        <v>2.5543</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.8637</v>
+        <v>-0.8718</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3179</v>
+        <v>-1.2888</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.4966</v>
+        <v>-1.48</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q25" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0174</v>
+        <v>-0.6178</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.747</v>
+        <v>-0.156</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2704</v>
+        <v>-0.4618</v>
       </c>
       <c r="V25" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W25" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.8109</v>
+        <v>-11.8078</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.120800000000001</v>
+        <v>-9.4214</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.6903</v>
+        <v>-2.3863</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.438400000000001</v>
+        <v>-6.4412</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.906999999999999</v>
+        <v>-2.9418</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.5316</v>
+        <v>-3.4992</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5071</v>
+        <v>3.283700000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>1.748600000000001</v>
+        <v>1.5884</v>
       </c>
       <c r="L26" t="n">
-        <v>1.758799999999999</v>
+        <v>1.6953</v>
       </c>
       <c r="M26" t="n">
-        <v>-9.9459</v>
+        <v>-9.7248</v>
       </c>
       <c r="N26" t="n">
-        <v>-4.6555</v>
+        <v>-4.5304</v>
       </c>
       <c r="O26" t="n">
-        <v>-5.290399999999999</v>
+        <v>-5.1945</v>
       </c>
       <c r="P26" t="n">
-        <v>3.4025</v>
+        <v>3.414499999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-17.0125</v>
+        <v>-17.0725</v>
       </c>
       <c r="R26" t="n">
-        <v>20.415</v>
+        <v>20.4868</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.5689</v>
+        <v>-3.5777</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0455000000000001</v>
+        <v>0.06599999999999986</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.6143</v>
+        <v>-3.6435</v>
       </c>
       <c r="V26" t="n">
-        <v>-5.206</v>
+        <v>-5.203100000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>4.3389</v>
+        <v>4.3014</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.544900000000002</v>
+        <v>-9.5045</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104558_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104558_W12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.018</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-4.3013</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104558_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-9.5045</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
